--- a/artfynd/A 59119-2025 artfynd.xlsx
+++ b/artfynd/A 59119-2025 artfynd.xlsx
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56651230</v>
+        <v>181490</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>98053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222112</v>
+        <v>165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Månlåsbräken</t>
+          <t>Topplåsbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Botrychium lunaria</t>
+          <t>Botrychium lanceolatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Sw.</t>
+          <t>(S. G. Gmel.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tumsjövallen, Hjd</t>
+          <t>Tumsjövallen, ca 5,2, km norr om Hedeviken, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>432512</v>
+        <v>432507</v>
       </c>
       <c r="R2" t="n">
-        <v>6925721</v>
+        <v>6925735</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -738,14 +741,24 @@
           <t>Hede</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Z-Här-2020</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1965-01-01</t>
+          <t>1986-07-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1994-12-31</t>
+          <t>1986-07-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>620 möh. Coll.-Nr 752. Summer farm Trumvallen, among grasses. Något skumt, i Hd-floran nämns Tumsjövallen i Hede fs, Trumvallen ligger i Vemdalens fs. Ca 600 m.ö.h.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,15 +770,20 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Kulturmark</t>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>Uppsala-Evolutionsmuseet</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>V-45043</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Z Län Floraväktarna</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -775,59 +793,51 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Härjedalens kärlväxtflora 1994</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>181490</v>
+        <v>56651230</v>
       </c>
       <c r="B3" t="n">
-        <v>95594</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>98050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165</v>
+        <v>222112</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Topplåsbräken</t>
+          <t>Månlåsbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Botrychium lanceolatum</t>
+          <t>Botrychium lunaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(S. G. Gmel.) Ångstr.</t>
+          <t>(L.) Sw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tumsjövallen, ca 5,2, km norr om Hedeviken, Hjd</t>
+          <t>Tumsjövallen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432506.857252351</v>
+        <v>432512</v>
       </c>
       <c r="R3" t="n">
-        <v>6925735.460110359</v>
+        <v>6925721</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -852,34 +862,14 @@
           <t>Hede</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>Z-Här-2020</t>
-        </is>
-      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1986-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1965-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1986-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>620 möh. Coll.-Nr 752. Summer farm Trumvallen, among grasses. Något skumt, i Hd-floran nämns Tumsjövallen i Hede fs, Trumvallen ligger i Vemdalens fs. Ca 600 m.ö.h.</t>
+          <t>1994-12-31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,20 +881,15 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>Uppsala-Evolutionsmuseet</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>V-45043</t>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Kulturmark</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Z Län Floraväktarna</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
@@ -914,7 +899,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Floraväkteri Sverige</t>
+          <t>Härjedalens kärlväxtflora 1994</t>
         </is>
       </c>
     </row>
